--- a/hardware/pcb/controller_board/assembly/BOM_with_all_Digi_Key_numbers.xlsx
+++ b/hardware/pcb/controller_board/assembly/BOM_with_all_Digi_Key_numbers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukasnoll/Documents/builds/RobotArm/ExArm/hardware/pcb/controller_board/assembly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636C7F9B-E117-CF41-9EF7-8675371501D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BF1857-8F81-5F49-B4A4-383D7ED1EC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="38400" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="34200" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="232">
   <si>
     <t>BOM_with_all_Digi_Key_numbers</t>
   </si>
@@ -560,9 +560,6 @@
     <t>CONN HEADER VERT 8POS 3MM</t>
   </si>
   <si>
-    <t>3310209 MOLEX</t>
-  </si>
-  <si>
     <t>CONN HEADER VERT 4POS 2.54MM</t>
   </si>
   <si>
@@ -581,9 +578,6 @@
     <t>CONN HEADER VERT 3POS 3MM</t>
   </si>
   <si>
-    <t>0436500328</t>
-  </si>
-  <si>
     <t>in set</t>
   </si>
   <si>
@@ -717,6 +711,24 @@
   </si>
   <si>
     <t>SUM</t>
+  </si>
+  <si>
+    <t>10127721-082LF</t>
+  </si>
+  <si>
+    <t>66200311122</t>
+  </si>
+  <si>
+    <t>missed (1nF)</t>
+  </si>
+  <si>
+    <t>missed (65pF)</t>
+  </si>
+  <si>
+    <t>need more</t>
+  </si>
+  <si>
+    <t>out</t>
   </si>
 </sst>
 </file>
@@ -736,12 +748,14 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -945,9 +959,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -981,11 +992,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2158,21 +2172,21 @@
     <col min="5" max="5" width="11.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="33.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" style="20" customWidth="1"/>
     <col min="9" max="9" width="8.33203125" style="1"/>
     <col min="10" max="10" width="15.83203125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
@@ -2190,19 +2204,19 @@
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="16" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2223,17 +2237,17 @@
         <v>9</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="23">
         <v>5</v>
       </c>
-      <c r="I3" s="23">
-        <f>H3*C3</f>
+      <c r="I3" s="22">
+        <f t="shared" ref="I3:I11" si="0">H3*C3</f>
         <v>5</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="23" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2257,14 +2271,14 @@
       <c r="G4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="22">
         <v>0.33</v>
       </c>
-      <c r="I4" s="23">
-        <f>H4*C4</f>
+      <c r="I4" s="22">
+        <f t="shared" si="0"/>
         <v>1.32</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2278,26 +2292,26 @@
       <c r="C5" s="10">
         <v>4</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="24" t="s">
         <v>146</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="22">
         <v>0.22</v>
       </c>
-      <c r="I5" s="23">
-        <f>H5*C5</f>
+      <c r="I5" s="22">
+        <f t="shared" si="0"/>
         <v>0.88</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="22" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2317,20 +2331,20 @@
       <c r="E6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="23">
-        <f>H6*C6</f>
+      <c r="I6" s="22">
+        <f t="shared" si="0"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2350,21 +2364,21 @@
       <c r="E7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>158</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="I7" s="23">
-        <f>H7*C7</f>
+      <c r="I7" s="22">
+        <f t="shared" si="0"/>
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="J7" s="24" t="s">
-        <v>139</v>
+      <c r="J7" s="23" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2381,21 +2395,21 @@
         <v>23</v>
       </c>
       <c r="E8" s="14"/>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="22">
         <v>0.15</v>
       </c>
-      <c r="I8" s="23">
-        <f>H8*C8</f>
+      <c r="I8" s="22">
+        <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
-      <c r="J8" s="24" t="s">
-        <v>139</v>
+      <c r="J8" s="23" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2412,20 +2426,20 @@
         <v>25</v>
       </c>
       <c r="E9" s="14"/>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="22">
         <v>5.5E-2</v>
       </c>
-      <c r="I9" s="23">
-        <f>H9*C9</f>
+      <c r="I9" s="22">
+        <f t="shared" si="0"/>
         <v>0.22</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2447,15 +2461,15 @@
       <c r="G10" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="22">
         <v>1.2E-2</v>
       </c>
-      <c r="I10" s="23">
-        <f>H10*C10</f>
+      <c r="I10" s="22">
+        <f t="shared" si="0"/>
         <v>0.27600000000000002</v>
       </c>
-      <c r="J10" s="24" t="s">
-        <v>139</v>
+      <c r="J10" s="23" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2476,14 +2490,14 @@
       <c r="G11" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="22">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I11" s="23">
-        <f>H11*C11</f>
+      <c r="I11" s="22">
+        <f t="shared" si="0"/>
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2504,17 +2518,17 @@
         <v>15</v>
       </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="I12" s="23">
-        <f t="shared" ref="I12:I28" si="0">H12*C12</f>
+      <c r="I12" s="22">
+        <f t="shared" ref="I12:I28" si="1">H12*C12</f>
         <v>0.12</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="23" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2538,14 +2552,14 @@
       <c r="G13" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="22">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="I13" s="23">
-        <f t="shared" si="0"/>
+      <c r="I13" s="22">
+        <f t="shared" si="1"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2567,14 +2581,14 @@
       <c r="G14" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="22">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I14" s="23">
-        <f t="shared" si="0"/>
+      <c r="I14" s="22">
+        <f t="shared" si="1"/>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2592,20 +2606,20 @@
         <v>36</v>
       </c>
       <c r="E15" s="14"/>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="17" t="s">
         <v>156</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="22">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="I15" s="23">
-        <f t="shared" si="0"/>
+      <c r="I15" s="22">
+        <f t="shared" si="1"/>
         <v>0.22799999999999998</v>
       </c>
-      <c r="J15" s="24" t="s">
+      <c r="J15" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2623,20 +2637,20 @@
         <v>38</v>
       </c>
       <c r="E16" s="14"/>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="17" t="s">
         <v>159</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="I16" s="23">
-        <f t="shared" si="0"/>
+      <c r="I16" s="22">
+        <f t="shared" si="1"/>
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2658,14 +2672,14 @@
       <c r="G17" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="23">
         <v>0.4</v>
       </c>
-      <c r="I17" s="23">
-        <f t="shared" si="0"/>
+      <c r="I17" s="22">
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2679,7 +2693,7 @@
       <c r="C18" s="10">
         <v>15</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="24" t="s">
         <v>44</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -2688,17 +2702,17 @@
       <c r="F18" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="22">
         <v>0.21</v>
       </c>
-      <c r="I18" s="23">
-        <f t="shared" si="0"/>
+      <c r="I18" s="22">
+        <f t="shared" si="1"/>
         <v>3.15</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2706,7 +2720,7 @@
       <c r="A19" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>164</v>
       </c>
       <c r="C19" s="10">
@@ -2719,17 +2733,17 @@
         <v>49</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="22">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I19" s="23">
-        <f t="shared" si="0"/>
+      <c r="I19" s="22">
+        <f t="shared" si="1"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2749,20 +2763,20 @@
       <c r="E20" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="17" t="s">
         <v>166</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="22">
         <v>0.19800000000000001</v>
       </c>
-      <c r="I20" s="23">
-        <f t="shared" si="0"/>
+      <c r="I20" s="22">
+        <f t="shared" si="1"/>
         <v>0.59400000000000008</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2782,21 +2796,21 @@
       <c r="E21" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="22">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="I21" s="23">
-        <f t="shared" si="0"/>
+      <c r="I21" s="22">
+        <f t="shared" si="1"/>
         <v>0.53200000000000003</v>
       </c>
-      <c r="J21" s="24" t="s">
-        <v>139</v>
+      <c r="J21" s="23" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2819,14 +2833,14 @@
       <c r="G22" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="22">
         <v>6.3E-2</v>
       </c>
-      <c r="I22" s="23">
-        <f t="shared" si="0"/>
+      <c r="I22" s="22">
+        <f t="shared" si="1"/>
         <v>0.126</v>
       </c>
-      <c r="J22" s="24" t="s">
+      <c r="J22" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2850,14 +2864,14 @@
       <c r="G23" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="22">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="I23" s="23">
-        <f t="shared" si="0"/>
+      <c r="I23" s="22">
+        <f t="shared" si="1"/>
         <v>0.318</v>
       </c>
-      <c r="J23" s="24" t="s">
+      <c r="J23" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2877,20 +2891,20 @@
       <c r="E24" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="27" t="s">
-        <v>175</v>
+      <c r="F24" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="H24" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="I24" s="23">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="J24" s="24" t="s">
+      <c r="H24" s="22">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="I24" s="22">
+        <f t="shared" si="1"/>
+        <v>2.04</v>
+      </c>
+      <c r="J24" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2911,19 +2925,19 @@
         <v>64</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H25" s="23">
+        <v>179</v>
+      </c>
+      <c r="H25" s="22">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I25" s="23">
-        <f t="shared" si="0"/>
+      <c r="I25" s="22">
+        <f t="shared" si="1"/>
         <v>0.21499999999999997</v>
       </c>
-      <c r="J25" s="24" t="s">
+      <c r="J25" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2944,19 +2958,19 @@
         <v>64</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="23">
+        <v>179</v>
+      </c>
+      <c r="H26" s="22">
         <v>0.04</v>
       </c>
-      <c r="I26" s="23">
-        <f t="shared" si="0"/>
+      <c r="I26" s="22">
+        <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
-      <c r="J26" s="24" t="s">
+      <c r="J26" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2977,19 +2991,19 @@
         <v>64</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="23">
+        <v>178</v>
+      </c>
+      <c r="H27" s="22">
         <v>0.11</v>
       </c>
-      <c r="I27" s="23">
-        <f t="shared" si="0"/>
+      <c r="I27" s="22">
+        <f t="shared" si="1"/>
         <v>0.11</v>
       </c>
-      <c r="J27" s="24" t="s">
+      <c r="J27" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3010,19 +3024,19 @@
         <v>64</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" s="23">
+        <v>177</v>
+      </c>
+      <c r="H28" s="22">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="I28" s="23">
-        <f t="shared" si="0"/>
+      <c r="I28" s="22">
+        <f t="shared" si="1"/>
         <v>0.27</v>
       </c>
-      <c r="J28" s="24" t="s">
+      <c r="J28" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3043,19 +3057,19 @@
         <v>75</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="H29" s="23">
-        <v>0.85899999999999999</v>
-      </c>
-      <c r="I29" s="23">
-        <f t="shared" ref="I29:I55" si="1">H29*C29</f>
-        <v>5.1539999999999999</v>
-      </c>
-      <c r="J29" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="H29" s="22">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="I29" s="22">
+        <f t="shared" ref="I29:I55" si="2">H29*C29</f>
+        <v>1.6440000000000001</v>
+      </c>
+      <c r="J29" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3073,16 +3087,16 @@
         <v>78</v>
       </c>
       <c r="E30" s="14"/>
-      <c r="F30" s="18" t="s">
-        <v>183</v>
+      <c r="F30" s="17" t="s">
+        <v>181</v>
       </c>
       <c r="G30" s="12"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23">
-        <f t="shared" si="1"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J30" s="24" t="s">
+      <c r="J30" s="23" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3101,19 +3115,19 @@
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H31" s="23">
+        <v>182</v>
+      </c>
+      <c r="H31" s="22">
         <v>1.28</v>
       </c>
-      <c r="I31" s="23">
-        <f t="shared" si="1"/>
+      <c r="I31" s="22">
+        <f t="shared" si="2"/>
         <v>3.84</v>
       </c>
-      <c r="J31" s="24" t="s">
+      <c r="J31" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3132,17 +3146,17 @@
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G32" s="12"/>
-      <c r="H32" s="23">
+      <c r="H32" s="22">
         <v>2.21</v>
       </c>
-      <c r="I32" s="23">
-        <f t="shared" si="1"/>
+      <c r="I32" s="22">
+        <f t="shared" si="2"/>
         <v>2.21</v>
       </c>
-      <c r="J32" s="24" t="s">
+      <c r="J32" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3160,18 +3174,18 @@
         <v>7447709470</v>
       </c>
       <c r="E33" s="14"/>
-      <c r="F33" s="18" t="s">
-        <v>187</v>
+      <c r="F33" s="17" t="s">
+        <v>185</v>
       </c>
       <c r="G33" s="12"/>
-      <c r="H33" s="23">
+      <c r="H33" s="22">
         <v>2.21</v>
       </c>
-      <c r="I33" s="23">
-        <f t="shared" si="1"/>
+      <c r="I33" s="22">
+        <f t="shared" si="2"/>
         <v>2.21</v>
       </c>
-      <c r="J33" s="24" t="s">
+      <c r="J33" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3190,19 +3204,19 @@
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="H34" s="23">
+        <v>186</v>
+      </c>
+      <c r="H34" s="22">
         <v>0.2</v>
       </c>
-      <c r="I34" s="23">
-        <f t="shared" si="1"/>
+      <c r="I34" s="22">
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="J34" s="24" t="s">
+      <c r="J34" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3221,19 +3235,19 @@
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="H35" s="23">
+        <v>189</v>
+      </c>
+      <c r="H35" s="22">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="I35" s="23">
-        <f t="shared" si="1"/>
+      <c r="I35" s="22">
+        <f t="shared" si="2"/>
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="J35" s="24" t="s">
+      <c r="J35" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3252,19 +3266,19 @@
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H36" s="23">
+        <v>191</v>
+      </c>
+      <c r="H36" s="22">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="I36" s="23">
-        <f t="shared" si="1"/>
+      <c r="I36" s="22">
+        <f t="shared" si="2"/>
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="J36" s="24" t="s">
+      <c r="J36" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3283,19 +3297,19 @@
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="H37" s="23">
+        <v>193</v>
+      </c>
+      <c r="H37" s="22">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I37" s="23">
-        <f t="shared" si="1"/>
+      <c r="I37" s="22">
+        <f t="shared" si="2"/>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J37" s="24" t="s">
+      <c r="J37" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3314,19 +3328,19 @@
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="H38" s="23">
+        <v>195</v>
+      </c>
+      <c r="H38" s="22">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I38" s="23">
-        <f t="shared" si="1"/>
+      <c r="I38" s="22">
+        <f t="shared" si="2"/>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J38" s="24" t="s">
+      <c r="J38" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3345,19 +3359,19 @@
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="H39" s="23">
+        <v>197</v>
+      </c>
+      <c r="H39" s="22">
         <v>1.12E-2</v>
       </c>
-      <c r="I39" s="23">
-        <f t="shared" si="1"/>
+      <c r="I39" s="22">
+        <f t="shared" si="2"/>
         <v>0.2016</v>
       </c>
-      <c r="J39" s="24" t="s">
+      <c r="J39" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3376,19 +3390,19 @@
       </c>
       <c r="E40" s="14"/>
       <c r="F40" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="H40" s="23">
+        <v>199</v>
+      </c>
+      <c r="H40" s="22">
         <v>0.01</v>
       </c>
-      <c r="I40" s="23">
-        <f t="shared" si="1"/>
+      <c r="I40" s="22">
+        <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
-      <c r="J40" s="24" t="s">
+      <c r="J40" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3407,19 +3421,19 @@
       </c>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="H41" s="23">
+        <v>201</v>
+      </c>
+      <c r="H41" s="22">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="I41" s="23">
-        <f t="shared" si="1"/>
+      <c r="I41" s="22">
+        <f t="shared" si="2"/>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="J41" s="24" t="s">
+      <c r="J41" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3438,19 +3452,19 @@
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="H42" s="23">
+        <v>203</v>
+      </c>
+      <c r="H42" s="22">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="I42" s="23">
-        <f t="shared" si="1"/>
+      <c r="I42" s="22">
+        <f t="shared" si="2"/>
         <v>0.156</v>
       </c>
-      <c r="J42" s="24" t="s">
+      <c r="J42" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3469,19 +3483,19 @@
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="H43" s="23">
+        <v>205</v>
+      </c>
+      <c r="H43" s="22">
         <v>2.4E-2</v>
       </c>
-      <c r="I43" s="23">
-        <f t="shared" si="1"/>
+      <c r="I43" s="22">
+        <f t="shared" si="2"/>
         <v>7.2000000000000008E-2</v>
       </c>
-      <c r="J43" s="24" t="s">
+      <c r="J43" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3501,12 +3515,12 @@
       <c r="E44" s="14"/>
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23">
-        <f t="shared" si="1"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J44" s="24" t="s">
+      <c r="J44" s="23" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3525,19 +3539,19 @@
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="H45" s="23">
+        <v>207</v>
+      </c>
+      <c r="H45" s="22">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="I45" s="23">
-        <f t="shared" si="1"/>
+      <c r="I45" s="22">
+        <f t="shared" si="2"/>
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="J45" s="24" t="s">
+      <c r="J45" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3556,19 +3570,19 @@
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="H46" s="23">
+        <v>209</v>
+      </c>
+      <c r="H46" s="22">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="I46" s="23">
-        <f t="shared" si="1"/>
+      <c r="I46" s="22">
+        <f t="shared" si="2"/>
         <v>6.3E-2</v>
       </c>
-      <c r="J46" s="24" t="s">
+      <c r="J46" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3587,19 +3601,19 @@
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="H47" s="23">
+        <v>213</v>
+      </c>
+      <c r="H47" s="22">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I47" s="23">
-        <f t="shared" si="1"/>
+      <c r="I47" s="22">
+        <f t="shared" si="2"/>
         <v>0.10500000000000001</v>
       </c>
-      <c r="J47" s="24" t="s">
+      <c r="J47" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3618,19 +3632,19 @@
       </c>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="H48" s="23">
+        <v>211</v>
+      </c>
+      <c r="H48" s="22">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="I48" s="23">
-        <f t="shared" si="1"/>
+      <c r="I48" s="22">
+        <f t="shared" si="2"/>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="J48" s="24" t="s">
+      <c r="J48" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3649,19 +3663,19 @@
       </c>
       <c r="E49" s="14"/>
       <c r="F49" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="H49" s="23">
+        <v>215</v>
+      </c>
+      <c r="H49" s="22">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I49" s="23">
-        <f t="shared" si="1"/>
+      <c r="I49" s="22">
+        <f t="shared" si="2"/>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="J49" s="24" t="s">
+      <c r="J49" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3680,19 +3694,19 @@
       </c>
       <c r="E50" s="14"/>
       <c r="F50" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="H50" s="23">
+        <v>217</v>
+      </c>
+      <c r="H50" s="22">
         <v>0.123</v>
       </c>
-      <c r="I50" s="23">
-        <f t="shared" si="1"/>
+      <c r="I50" s="22">
+        <f t="shared" si="2"/>
         <v>0.246</v>
       </c>
-      <c r="J50" s="24" t="s">
+      <c r="J50" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3713,19 +3727,19 @@
         <v>118</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="H51" s="23">
+        <v>219</v>
+      </c>
+      <c r="H51" s="22">
         <v>3.33</v>
       </c>
-      <c r="I51" s="23">
-        <f t="shared" si="1"/>
+      <c r="I51" s="22">
+        <f t="shared" si="2"/>
         <v>6.66</v>
       </c>
-      <c r="J51" s="24" t="s">
+      <c r="J51" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3746,19 +3760,19 @@
         <v>122</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="H52" s="23">
+        <v>221</v>
+      </c>
+      <c r="H52" s="22">
         <v>0.36899999999999999</v>
       </c>
-      <c r="I52" s="23">
-        <f t="shared" si="1"/>
+      <c r="I52" s="22">
+        <f t="shared" si="2"/>
         <v>1.845</v>
       </c>
-      <c r="J52" s="24" t="s">
+      <c r="J52" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3777,19 +3791,19 @@
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="H53" s="23">
+      <c r="H53" s="22">
         <v>1.8009999999999999</v>
       </c>
-      <c r="I53" s="23">
-        <f t="shared" si="1"/>
+      <c r="I53" s="22">
+        <f t="shared" si="2"/>
         <v>10.805999999999999</v>
       </c>
-      <c r="J53" s="24" t="s">
+      <c r="J53" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3808,17 +3822,17 @@
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23">
-        <f t="shared" si="1"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J54" s="24" t="s">
+      <c r="J54" s="23" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3839,29 +3853,29 @@
         <v>132</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G55" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="H55" s="23">
+      <c r="H55" s="22">
         <v>1.5</v>
       </c>
-      <c r="I55" s="23">
-        <f t="shared" si="1"/>
+      <c r="I55" s="22">
+        <f t="shared" si="2"/>
         <v>4.5</v>
       </c>
-      <c r="J55" s="24" t="s">
+      <c r="J55" s="23" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H56" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="I56" s="20">
+      <c r="H56" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="I56" s="19">
         <f>SUM(I3:I55)</f>
-        <v>59.845600000000005</v>
+        <v>52.375599999999991</v>
       </c>
     </row>
   </sheetData>
